--- a/0_0_Data/3_Naive_Forecaster_Data/1_YoY_Forecast_Vectors/forecast_series_PRIVCON_yoy_AVERAGE_1_9_summer.xlsx
+++ b/0_0_Data/3_Naive_Forecaster_Data/1_YoY_Forecast_Vectors/forecast_series_PRIVCON_yoy_AVERAGE_1_9_summer.xlsx
@@ -392,7 +392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -414,305 +414,350 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>39583</v>
+        <v>38496</v>
       </c>
       <c r="B2">
-        <v>2008</v>
+        <v>2005</v>
       </c>
       <c r="D2">
-        <v>2009</v>
-      </c>
-      <c r="E2">
-        <v>1.265019766896436</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>39948</v>
+        <v>38860</v>
       </c>
       <c r="B3">
-        <v>2009</v>
-      </c>
-      <c r="C3">
-        <v>0.337821977117625</v>
+        <v>2006</v>
       </c>
       <c r="D3">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="E3">
-        <v>1.858657482882586</v>
+        <v>2.464406476915149</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>40310</v>
+        <v>39226</v>
       </c>
       <c r="B4">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="C4">
-        <v>-1.890773121057054</v>
+        <v>3.701949943713156</v>
       </c>
       <c r="D4">
-        <v>2011</v>
+        <v>2008</v>
       </c>
       <c r="E4">
-        <v>-3.246097549514837</v>
+        <v>8.664288130980768</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>40676</v>
+        <v>39595</v>
       </c>
       <c r="B5">
-        <v>2011</v>
+        <v>2008</v>
       </c>
       <c r="C5">
-        <v>1.891565607550105</v>
+        <v>2.071027795385527</v>
       </c>
       <c r="D5">
-        <v>2012</v>
+        <v>2009</v>
       </c>
       <c r="E5">
-        <v>1.609625625600009</v>
+        <v>5.125423150176811</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>41044</v>
+        <v>39959</v>
       </c>
       <c r="B6">
-        <v>2012</v>
+        <v>2009</v>
       </c>
       <c r="C6">
-        <v>1.113165545862116</v>
+        <v>0.8793178469574725</v>
       </c>
       <c r="D6">
-        <v>2013</v>
+        <v>2010</v>
       </c>
       <c r="E6">
-        <v>1.609625625599986</v>
+        <v>1.013743251195054</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>41409</v>
+        <v>40319</v>
       </c>
       <c r="B7">
-        <v>2013</v>
+        <v>2010</v>
       </c>
       <c r="C7">
-        <v>1.070385798714391</v>
+        <v>2.722714748034383</v>
       </c>
       <c r="D7">
-        <v>2014</v>
+        <v>2011</v>
       </c>
       <c r="E7">
-        <v>3.238605209600021</v>
+        <v>4.356945153942826</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>41774</v>
+        <v>40687</v>
       </c>
       <c r="B8">
-        <v>2014</v>
+        <v>2011</v>
       </c>
       <c r="C8">
-        <v>1.384186838979828</v>
+        <v>2.432032972462994</v>
       </c>
       <c r="D8">
-        <v>2015</v>
+        <v>2012</v>
       </c>
       <c r="E8">
-        <v>2.777885851461526</v>
+        <v>5.259901377404663</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>42137</v>
+        <v>41053</v>
       </c>
       <c r="B9">
-        <v>2015</v>
+        <v>2012</v>
       </c>
       <c r="C9">
-        <v>2.349355943833076</v>
+        <v>1.446803774865346</v>
       </c>
       <c r="D9">
-        <v>2016</v>
+        <v>2013</v>
       </c>
       <c r="E9">
-        <v>2.436566844071941</v>
+        <v>0.7814544160914094</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>42503</v>
+        <v>41418</v>
       </c>
       <c r="B10">
-        <v>2016</v>
+        <v>2013</v>
       </c>
       <c r="C10">
-        <v>1.78642563555842</v>
+        <v>0.3505172185931382</v>
       </c>
       <c r="D10">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="E10">
-        <v>1.694971351092267</v>
+        <v>-0.563230141139015</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>42867</v>
+        <v>41782</v>
       </c>
       <c r="B11">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="C11">
-        <v>1.331333081915509</v>
+        <v>0.673698994709393</v>
       </c>
       <c r="D11">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="E11">
-        <v>1.216098605743343</v>
+        <v>1.713328878049047</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>43235</v>
+        <v>42146</v>
       </c>
       <c r="B12">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="C12">
-        <v>1.282262557986469</v>
+        <v>2.178108891613229</v>
       </c>
       <c r="D12">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="E12">
-        <v>1.784618024189033</v>
+        <v>2.743139622505342</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>43600</v>
+        <v>42514</v>
       </c>
       <c r="B13">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="C13">
-        <v>2.247109253368307</v>
+        <v>2.624199977941988</v>
       </c>
       <c r="D13">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="E13">
-        <v>4.887093273600018</v>
+        <v>1.891200602579302</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>43966</v>
+        <v>42878</v>
       </c>
       <c r="B14">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="C14">
-        <v>-4.247034401476779</v>
+        <v>1.714647081576248</v>
       </c>
       <c r="D14">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="E14">
-        <v>-12.19860234240002</v>
+        <v>1.68734778233004</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>44341</v>
+        <v>43244</v>
       </c>
       <c r="B15">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="C15">
-        <v>-8.773175314851734</v>
+        <v>0.3317863932586596</v>
       </c>
       <c r="D15">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="E15">
-        <v>-19.76612614777711</v>
+        <v>-2.079831907815233</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>44706</v>
+        <v>43608</v>
       </c>
       <c r="B16">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="C16">
-        <v>3.555435198576862</v>
+        <v>0.9803420752674485</v>
       </c>
       <c r="D16">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="E16">
-        <v>-0.5376914776811237</v>
+        <v>-1.060771667791693</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>45071</v>
+        <v>43976</v>
       </c>
       <c r="B17">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="C17">
-        <v>-2.16280394131193</v>
+        <v>1.961124357427302</v>
       </c>
       <c r="D17">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="E17">
-        <v>-4.829433539906869</v>
+        <v>0.8241099463141222</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>45436</v>
+        <v>44341</v>
       </c>
       <c r="B18">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="C18">
-        <v>-0.244366674180263</v>
+        <v>2.091439143230134</v>
       </c>
       <c r="D18">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="E18">
-        <v>-1.64927836088965</v>
+        <v>0.8024032016000104</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
+        <v>44706</v>
+      </c>
+      <c r="B19">
+        <v>2022</v>
+      </c>
+      <c r="C19">
+        <v>0.06634141764301216</v>
+      </c>
+      <c r="D19">
+        <v>2023</v>
+      </c>
+      <c r="E19">
+        <v>0.2741132537363411</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="2">
+        <v>45071</v>
+      </c>
+      <c r="B20">
+        <v>2023</v>
+      </c>
+      <c r="C20">
+        <v>-7.337826364178824</v>
+      </c>
+      <c r="D20">
+        <v>2024</v>
+      </c>
+      <c r="E20">
+        <v>-18.16135672608771</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="2">
+        <v>45436</v>
+      </c>
+      <c r="B21">
+        <v>2024</v>
+      </c>
+      <c r="C21">
+        <v>0.6782221590200921</v>
+      </c>
+      <c r="D21">
+        <v>2025</v>
+      </c>
+      <c r="E21">
+        <v>-1.69663885654836</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="2">
         <v>45800</v>
       </c>
-      <c r="B19">
+      <c r="B22">
         <v>2025</v>
       </c>
-      <c r="C19">
-        <v>1.211873835667365</v>
-      </c>
-      <c r="D19">
+      <c r="C22">
+        <v>1.643639910449846</v>
+      </c>
+      <c r="D22">
         <v>2026</v>
       </c>
-      <c r="E19">
-        <v>1.973770215219273</v>
+      <c r="E22">
+        <v>-1.36234030734832</v>
       </c>
     </row>
   </sheetData>
